--- a/files/九龙-将军澳-海瑅湾 I.xlsx
+++ b/files/九龙-将军澳-海瑅湾 I.xlsx
@@ -18689,27 +18689,23 @@
       </c>
       <c r="F381" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H381" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I381" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="H381" s="5" t="n">
+        <v>12289000</v>
+      </c>
+      <c r="I381" s="5" t="n">
+        <v>20080</v>
       </c>
       <c r="J381" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -62739,7 +62735,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>132 套</t>
+          <t>131 套</t>
         </is>
       </c>
       <c r="C3" s="13" t="inlineStr">
@@ -62749,7 +62745,7 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>254 套</t>
+          <t>255 套</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -63833,12 +63829,12 @@
           <t>51/F</t>
         </is>
       </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>A | 612呎 (2房)
-招标单位
--
-(在售)</t>
+$1,229万
+$20,080/呎
+(26年-07月)</t>
         </is>
       </c>
       <c r="C22" s="18" t="inlineStr">

--- a/files/九龙-将军澳-海瑅湾 I.xlsx
+++ b/files/九龙-将军澳-海瑅湾 I.xlsx
@@ -673,7 +673,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -20274,7 +20274,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H414" s="5" t="n">
@@ -28002,7 +28002,7 @@
       </c>
       <c r="G582" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H582" s="5" t="n">
@@ -28922,7 +28922,7 @@
       </c>
       <c r="G602" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H602" s="5" t="n">
@@ -46304,14 +46304,14 @@
       </c>
       <c r="G975" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H975" s="5" t="n">
-        <v>7723900</v>
+        <v>6716000</v>
       </c>
       <c r="I975" s="5" t="n">
-        <v>17126</v>
+        <v>14891</v>
       </c>
       <c r="J975" s="3" t="inlineStr">
         <is>
@@ -46634,7 +46634,7 @@
       </c>
       <c r="G982" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H982" s="5" t="n">
@@ -46680,7 +46680,7 @@
       </c>
       <c r="G983" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H983" s="5" t="n">
@@ -64224,7 +64224,7 @@
           <t>C | 584呎 (2房)
 $1075万
 $18,409/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E26" s="23" t="inlineStr">
@@ -65760,7 +65760,7 @@
           <t>C | 584呎 (2房)
 $1072万
 $18,361/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E50" s="23" t="inlineStr">
@@ -65960,7 +65960,7 @@
           <t>D | 463呎 (2房)
 $790万
 $17,053/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F53" s="22" t="inlineStr">
@@ -69753,9 +69753,9 @@
       <c r="G12" s="22" t="inlineStr">
         <is>
           <t>F | 451呎 (2房)
-$772万
-$17,126/呎
-(26年-06月)</t>
+$672万
+$14,891/呎
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -69794,7 +69794,7 @@
           <t>D | 558呎 (2房)
 $988万
 $17,709/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -69802,7 +69802,7 @@
           <t>E | 452呎 (2房)
 $810万
 $17,911/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="G13" s="23" t="inlineStr">
